--- a/artfynd/A 54276-2023 artfynd.xlsx
+++ b/artfynd/A 54276-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54276-2023 artfynd.xlsx
+++ b/artfynd/A 54276-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,6 +1672,321 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124103598</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjöarbergskojan, Sjöarbergskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>477511</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6852060</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124102788</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjöarbergskojan, Sjöarbergskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>477499</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6852097</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonathan Blässar</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonathan Blässar</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124101503</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78789</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sjöarbergskojan, Sjöarbergskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>477528</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6852084</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jonathan Blässar</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jonathan Blässar</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54276-2023 artfynd.xlsx
+++ b/artfynd/A 54276-2023 artfynd.xlsx
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124103598</v>
+        <v>124102788</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,50 +1686,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjöarbergskojan, Sjöarbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477511</v>
+        <v>477499</v>
       </c>
       <c r="R11" t="n">
-        <v>6852060</v>
+        <v>6852097</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1773,22 +1764,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonathan Blässar</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonathan Blässar</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124102788</v>
+        <v>124103598</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,41 +1788,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöarbergskojan, Sjöarbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477499</v>
+        <v>477511</v>
       </c>
       <c r="R12" t="n">
-        <v>6852097</v>
+        <v>6852060</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,12 +1875,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jonathan Blässar</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jonathan Blässar</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 54276-2023 artfynd.xlsx
+++ b/artfynd/A 54276-2023 artfynd.xlsx
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124102788</v>
+        <v>124101503</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78811</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,16 +1690,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477499</v>
+        <v>477528</v>
       </c>
       <c r="R11" t="n">
-        <v>6852097</v>
+        <v>6852084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124101503</v>
+        <v>124103598</v>
       </c>
       <c r="B12" t="n">
-        <v>78811</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,41 +1788,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöarbergskojan, Sjöarbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477528</v>
+        <v>477511</v>
       </c>
       <c r="R12" t="n">
-        <v>6852084</v>
+        <v>6852060</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1866,22 +1875,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jonathan Blässar</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jonathan Blässar</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124103598</v>
+        <v>124102788</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,50 +1899,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sjöarbergskojan, Sjöarbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477511</v>
+        <v>477499</v>
       </c>
       <c r="R13" t="n">
-        <v>6852060</v>
+        <v>6852097</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,12 +1977,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonathan Blässar</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonathan Blässar</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 54276-2023 artfynd.xlsx
+++ b/artfynd/A 54276-2023 artfynd.xlsx
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124101503</v>
+        <v>124102788</v>
       </c>
       <c r="B11" t="n">
-        <v>78811</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,16 +1690,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477528</v>
+        <v>477499</v>
       </c>
       <c r="R11" t="n">
-        <v>6852084</v>
+        <v>6852097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124102788</v>
+        <v>124101503</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78811</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,16 +1903,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477499</v>
+        <v>477528</v>
       </c>
       <c r="R13" t="n">
-        <v>6852097</v>
+        <v>6852084</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54276-2023 artfynd.xlsx
+++ b/artfynd/A 54276-2023 artfynd.xlsx
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124102788</v>
+        <v>124101503</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78811</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,16 +1690,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477499</v>
+        <v>477528</v>
       </c>
       <c r="R11" t="n">
-        <v>6852097</v>
+        <v>6852084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124101503</v>
+        <v>124102788</v>
       </c>
       <c r="B13" t="n">
-        <v>78811</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,16 +1903,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477528</v>
+        <v>477499</v>
       </c>
       <c r="R13" t="n">
-        <v>6852084</v>
+        <v>6852097</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54276-2023 artfynd.xlsx
+++ b/artfynd/A 54276-2023 artfynd.xlsx
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124101503</v>
+        <v>124102788</v>
       </c>
       <c r="B11" t="n">
-        <v>78811</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,16 +1690,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477528</v>
+        <v>477499</v>
       </c>
       <c r="R11" t="n">
-        <v>6852084</v>
+        <v>6852097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124103598</v>
+        <v>124101503</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78811</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,50 +1788,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöarbergskojan, Sjöarbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477511</v>
+        <v>477528</v>
       </c>
       <c r="R12" t="n">
-        <v>6852060</v>
+        <v>6852084</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,22 +1866,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonathan Blässar</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonathan Blässar</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124102788</v>
+        <v>124103598</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,41 +1890,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sjöarbergskojan, Sjöarbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477499</v>
+        <v>477511</v>
       </c>
       <c r="R13" t="n">
-        <v>6852097</v>
+        <v>6852060</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,12 +1977,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jonathan Blässar</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jonathan Blässar</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
